--- a/data/trans_bre/POLIPATOLOGIA_2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,67; 15,98</t>
+          <t>6,44; 14,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 23,84</t>
+          <t>13,06; 22,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 19,93</t>
+          <t>9,83; 19,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 13,9</t>
+          <t>-1,31; 13,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,81; 95,62</t>
+          <t>32,04; 87,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,82; 101,9</t>
+          <t>45,15; 95,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,83; 94,59</t>
+          <t>38,13; 93,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 40,08</t>
+          <t>-2,72; 39,59</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 18,34</t>
+          <t>9,61; 18,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 18,32</t>
+          <t>9,36; 18,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,74; 18,15</t>
+          <t>10,09; 18,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,9; 33,45</t>
+          <t>14,57; 33,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,72; 104,03</t>
+          <t>42,28; 98,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,57; 85,55</t>
+          <t>36,39; 84,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,27; 85,83</t>
+          <t>39,32; 87,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,87; 269,88</t>
+          <t>48,73; 247,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 22,16</t>
+          <t>12,59; 21,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 17,49</t>
+          <t>8,21; 17,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,57; 13,72</t>
+          <t>4,66; 13,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 44,08</t>
+          <t>8,9; 46,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,16; 125,63</t>
+          <t>56,77; 126,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,66; 91,63</t>
+          <t>34,18; 92,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,93; 69,95</t>
+          <t>18,86; 68,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 144,31</t>
+          <t>26,52; 166,59</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 16,63</t>
+          <t>8,5; 16,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,21; 17,48</t>
+          <t>9,05; 17,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,04; 14,96</t>
+          <t>6,74; 14,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 25,74</t>
+          <t>11,19; 27,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>42,97; 91,13</t>
+          <t>38,28; 89,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,92; 74,4</t>
+          <t>31,06; 74,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,97; 61,81</t>
+          <t>23,48; 59,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>29,21; 79,92</t>
+          <t>30,94; 84,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,66; 15,95</t>
+          <t>11,6; 15,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,2; 16,79</t>
+          <t>12,32; 16,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 14,35</t>
+          <t>9,9; 14,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,5; 28,84</t>
+          <t>13,35; 29,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,65; 84,85</t>
+          <t>55,88; 83,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,38; 72,08</t>
+          <t>48,55; 71,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,02; 62,54</t>
+          <t>39,74; 63,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,68; 109,04</t>
+          <t>40,34; 110,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_2-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_2-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,07</t>
+          <t>11,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 14,98</t>
+          <t>6,73; 15,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 22,76</t>
+          <t>12,71; 23,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,83; 19,81</t>
+          <t>10,02; 19,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 13,58</t>
+          <t>6,3; 16,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,04; 87,63</t>
+          <t>32,17; 95,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,15; 95,57</t>
+          <t>45,13; 101,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,13; 93,37</t>
+          <t>38,77; 92,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 39,59</t>
+          <t>16,08; 48,83</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22,1</t>
+          <t>16,55</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 18,1</t>
+          <t>10,08; 17,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,36; 18,43</t>
+          <t>9,19; 17,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 18,49</t>
+          <t>9,91; 18,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,57; 33,55</t>
+          <t>12,33; 20,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>42,28; 98,86</t>
+          <t>45,82; 99,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,39; 84,03</t>
+          <t>36,77; 82,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,32; 87,4</t>
+          <t>40,47; 86,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,73; 247,9</t>
+          <t>39,36; 78,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,37</t>
+          <t>13,44</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,59; 21,9</t>
+          <t>12,35; 21,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,21; 17,76</t>
+          <t>7,88; 17,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,66; 13,54</t>
+          <t>4,41; 14,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,9; 46,84</t>
+          <t>8,55; 18,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,77; 126,44</t>
+          <t>56,15; 120,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,18; 92,16</t>
+          <t>32,18; 89,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,86; 68,36</t>
+          <t>18,88; 72,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,52; 166,59</t>
+          <t>22,74; 61,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,17</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>39,47%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,5; 16,47</t>
+          <t>8,92; 16,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 17,69</t>
+          <t>8,99; 17,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 14,71</t>
+          <t>6,55; 15,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 27,12</t>
+          <t>9,22; 17,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,28; 89,44</t>
+          <t>40,14; 89,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,06; 74,22</t>
+          <t>32,43; 75,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,48; 59,19</t>
+          <t>22,34; 60,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,94; 84,29</t>
+          <t>26,15; 55,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,87</t>
+          <t>13,85</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,6; 15,67</t>
+          <t>11,49; 15,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,69</t>
+          <t>12,27; 16,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 14,47</t>
+          <t>10,1; 14,4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,35; 29,39</t>
+          <t>11,45; 15,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,88; 83,27</t>
+          <t>55,13; 84,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,55; 71,48</t>
+          <t>48,18; 71,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,74; 63,23</t>
+          <t>40,48; 62,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>40,34; 110,2</t>
+          <t>33,85; 51,75</t>
         </is>
       </c>
     </row>
